--- a/Project_WBS_AI_Adaptive_Learning.xlsx
+++ b/Project_WBS_AI_Adaptive_Learning.xlsx
@@ -1604,9 +1604,9 @@
           <t>Task</t>
         </is>
       </c>
-      <c r="C11" s="82" t="n"/>
-      <c r="D11" s="82" t="n"/>
-      <c r="E11" s="83" t="n"/>
+      <c r="C11" s="51" t="n"/>
+      <c r="D11" s="51" t="n"/>
+      <c r="E11" s="52" t="n"/>
       <c r="F11" s="84" t="inlineStr">
         <is>
           <t>Start date</t>
@@ -1637,49 +1637,47 @@
           <t>W1</t>
         </is>
       </c>
-      <c r="L11" s="86" t="n"/>
-      <c r="M11" s="86" t="n"/>
-      <c r="N11" s="86" t="n"/>
-      <c r="O11" s="87" t="n"/>
+      <c r="L11" s="53" t="n"/>
+      <c r="M11" s="53" t="n"/>
+      <c r="N11" s="53" t="n"/>
+      <c r="O11" s="54" t="n"/>
       <c r="P11" s="84" t="inlineStr">
         <is>
           <t>W2</t>
         </is>
       </c>
-      <c r="Q11" s="86" t="n"/>
-      <c r="R11" s="86" t="n"/>
-      <c r="S11" s="86" t="n"/>
-      <c r="T11" s="87" t="n"/>
+      <c r="Q11" s="53" t="n"/>
+      <c r="R11" s="53" t="n"/>
+      <c r="S11" s="53" t="n"/>
+      <c r="T11" s="54" t="n"/>
       <c r="U11" s="84" t="inlineStr">
         <is>
           <t>W3</t>
         </is>
       </c>
-      <c r="V11" s="86" t="n"/>
-      <c r="W11" s="86" t="n"/>
-      <c r="X11" s="86" t="n"/>
-      <c r="Y11" s="87" t="n"/>
+      <c r="V11" s="53" t="n"/>
+      <c r="W11" s="53" t="n"/>
+      <c r="X11" s="53" t="n"/>
+      <c r="Y11" s="54" t="n"/>
       <c r="Z11" s="88" t="inlineStr">
         <is>
           <t>W4</t>
         </is>
       </c>
-      <c r="AA11" s="86" t="n"/>
-      <c r="AB11" s="86" t="n"/>
-      <c r="AC11" s="86" t="n"/>
-      <c r="AD11" s="89" t="n"/>
+      <c r="AA11" s="53" t="n"/>
+      <c r="AB11" s="53" t="n"/>
+      <c r="AC11" s="53" t="n"/>
+      <c r="AD11" s="56" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="70" t="n"/>
-      <c r="B12" s="90" t="n"/>
-      <c r="C12" s="70" t="n"/>
-      <c r="D12" s="70" t="n"/>
-      <c r="E12" s="91" t="n"/>
-      <c r="F12" s="92" t="n"/>
-      <c r="G12" s="92" t="n"/>
-      <c r="H12" s="92" t="n"/>
-      <c r="I12" s="92" t="n"/>
-      <c r="J12" s="93" t="n"/>
+      <c r="B12" s="57" t="n"/>
+      <c r="E12" s="58" t="n"/>
+      <c r="F12" s="59" t="n"/>
+      <c r="G12" s="59" t="n"/>
+      <c r="H12" s="59" t="n"/>
+      <c r="I12" s="59" t="n"/>
+      <c r="J12" s="60" t="n"/>
       <c r="K12" s="94" t="inlineStr">
         <is>
           <t>D1</t>
@@ -1783,15 +1781,15 @@
     </row>
     <row r="13">
       <c r="A13" s="70" t="n"/>
-      <c r="B13" s="97" t="n"/>
-      <c r="C13" s="98" t="n"/>
-      <c r="D13" s="98" t="n"/>
-      <c r="E13" s="99" t="n"/>
-      <c r="F13" s="100" t="n"/>
-      <c r="G13" s="100" t="n"/>
-      <c r="H13" s="100" t="n"/>
-      <c r="I13" s="100" t="n"/>
-      <c r="J13" s="101" t="n"/>
+      <c r="B13" s="61" t="n"/>
+      <c r="C13" s="62" t="n"/>
+      <c r="D13" s="62" t="n"/>
+      <c r="E13" s="63" t="n"/>
+      <c r="F13" s="64" t="n"/>
+      <c r="G13" s="64" t="n"/>
+      <c r="H13" s="64" t="n"/>
+      <c r="I13" s="64" t="n"/>
+      <c r="J13" s="65" t="n"/>
       <c r="K13" s="102" t="n">
         <v>46314</v>
       </c>
@@ -1969,11 +1967,7 @@
           <t>Khảo sát mô hình phân loại và recommender</t>
         </is>
       </c>
-      <c r="D16" s="106" t="inlineStr">
-        <is>
-          <t>1.1.1. Sub-title</t>
-        </is>
-      </c>
+      <c r="D16" s="106" t="n"/>
       <c r="E16" s="107" t="n"/>
       <c r="F16" s="108" t="n">
         <v>46316</v>
@@ -2026,11 +2020,7 @@
         </is>
       </c>
       <c r="D17" s="106" t="n"/>
-      <c r="E17" s="107" t="inlineStr">
-        <is>
-          <t>1.1.1.1. Sub-title</t>
-        </is>
-      </c>
+      <c r="E17" s="107" t="n"/>
       <c r="F17" s="108" t="n">
         <v>46317</v>
       </c>
